--- a/P1-R03-工期评估表-20260915.xlsx
+++ b/P1-R03-工期评估表-20260915.xlsx
@@ -19,13 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.##"/>
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="m/d"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="44">
     <font>
@@ -1848,7 +1847,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="76" t="inlineStr">
         <is>
@@ -2286,7 +2284,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="76" t="inlineStr">
         <is>
@@ -2551,7 +2548,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="76" t="inlineStr">
         <is>
@@ -2695,7 +2691,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="77" t="inlineStr">
         <is>
@@ -2763,7 +2758,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="77" t="inlineStr">
         <is>
@@ -7065,7 +7059,7 @@
       </c>
       <c r="J10" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K10" s="100" t="n">
@@ -7125,7 +7119,7 @@
       </c>
       <c r="J11" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K11" s="100" t="n">
@@ -7185,7 +7179,7 @@
       </c>
       <c r="J12" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K12" s="100" t="n">
@@ -7245,7 +7239,7 @@
       </c>
       <c r="J13" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K13" s="100" t="n">
@@ -7305,7 +7299,7 @@
       </c>
       <c r="J14" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K14" s="100" t="n">
@@ -7363,7 +7357,7 @@
       </c>
       <c r="J15" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K15" s="100" t="n"/>
@@ -7419,7 +7413,7 @@
       </c>
       <c r="J16" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K16" s="100" t="n">
@@ -7475,7 +7469,7 @@
       </c>
       <c r="J17" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K17" s="100" t="n">
@@ -7531,7 +7525,7 @@
       </c>
       <c r="J18" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K18" s="100" t="n">
@@ -7591,7 +7585,7 @@
       </c>
       <c r="J19" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K19" s="100" t="n">
@@ -7651,7 +7645,7 @@
       </c>
       <c r="J20" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K20" s="100" t="n">
@@ -7711,7 +7705,7 @@
       </c>
       <c r="J21" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K21" s="100" t="n">
@@ -7767,7 +7761,7 @@
       </c>
       <c r="J22" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K22" s="100" t="n">
@@ -7827,7 +7821,7 @@
       </c>
       <c r="J23" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K23" s="100" t="n">
@@ -7887,7 +7881,7 @@
       </c>
       <c r="J24" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K24" s="100" t="n">
@@ -7947,7 +7941,7 @@
       </c>
       <c r="J25" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K25" s="100" t="n">
@@ -8007,7 +8001,7 @@
       </c>
       <c r="J26" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K26" s="100" t="n">
@@ -8067,7 +8061,7 @@
       </c>
       <c r="J27" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K27" s="100" t="n">
@@ -8127,7 +8121,7 @@
       </c>
       <c r="J28" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K28" s="100" t="n">
@@ -8187,7 +8181,7 @@
       </c>
       <c r="J29" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K29" s="100" t="n">
@@ -8247,7 +8241,7 @@
       </c>
       <c r="J30" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K30" s="100" t="n">
@@ -8307,7 +8301,7 @@
       </c>
       <c r="J31" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K31" s="100" t="n">
@@ -8367,7 +8361,7 @@
       </c>
       <c r="J32" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K32" s="100" t="n">
@@ -8427,7 +8421,7 @@
       </c>
       <c r="J33" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K33" s="100" t="n">
@@ -8487,7 +8481,7 @@
       </c>
       <c r="J34" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K34" s="100" t="n">
@@ -8547,7 +8541,7 @@
       </c>
       <c r="J35" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K35" s="100" t="n">
@@ -8607,7 +8601,7 @@
       </c>
       <c r="J36" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K36" s="100" t="n">
@@ -8667,7 +8661,7 @@
       </c>
       <c r="J37" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K37" s="100" t="n">
@@ -8727,7 +8721,7 @@
       </c>
       <c r="J38" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K38" s="100" t="n">
@@ -8787,7 +8781,7 @@
       </c>
       <c r="J39" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K39" s="100" t="n">
@@ -8847,7 +8841,7 @@
       </c>
       <c r="J40" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K40" s="100" t="n">
@@ -8907,7 +8901,7 @@
       </c>
       <c r="J41" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K41" s="100" t="n">
@@ -8967,7 +8961,7 @@
       </c>
       <c r="J42" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K42" s="100" t="n">
@@ -9027,7 +9021,7 @@
       </c>
       <c r="J43" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K43" s="100" t="n">
@@ -9087,7 +9081,7 @@
       </c>
       <c r="J44" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K44" s="100" t="n">
@@ -9147,7 +9141,7 @@
       </c>
       <c r="J45" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K45" s="100" t="n">
@@ -9207,7 +9201,7 @@
       </c>
       <c r="J46" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K46" s="100" t="n">
@@ -9267,7 +9261,7 @@
       </c>
       <c r="J47" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K47" s="100" t="n">
@@ -9327,7 +9321,7 @@
       </c>
       <c r="J48" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K48" s="100" t="n">
@@ -9387,7 +9381,7 @@
       </c>
       <c r="J49" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K49" s="100" t="n">
@@ -9447,7 +9441,7 @@
       </c>
       <c r="J50" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K50" s="100" t="n">
@@ -9507,7 +9501,7 @@
       </c>
       <c r="J51" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K51" s="100" t="n">
@@ -9567,7 +9561,7 @@
       </c>
       <c r="J52" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K52" s="100" t="n">
@@ -9627,7 +9621,7 @@
       </c>
       <c r="J53" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K53" s="100" t="n">
@@ -9687,7 +9681,7 @@
       </c>
       <c r="J54" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K54" s="100" t="n">
@@ -9747,7 +9741,7 @@
       </c>
       <c r="J55" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K55" s="100" t="n">
@@ -9807,7 +9801,7 @@
       </c>
       <c r="J56" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K56" s="100" t="n">
@@ -9867,7 +9861,7 @@
       </c>
       <c r="J57" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K57" s="100" t="n">
@@ -9927,7 +9921,7 @@
       </c>
       <c r="J58" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K58" s="100" t="n">
@@ -9987,7 +9981,7 @@
       </c>
       <c r="J59" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K59" s="100" t="n">
@@ -10047,7 +10041,7 @@
       </c>
       <c r="J60" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K60" s="100" t="n">
@@ -10103,7 +10097,7 @@
       </c>
       <c r="J61" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K61" s="100" t="n">
@@ -10163,7 +10157,7 @@
       </c>
       <c r="J62" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K62" s="100" t="n">
@@ -10219,7 +10213,7 @@
       </c>
       <c r="J63" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K63" s="100" t="n">
@@ -10279,7 +10273,7 @@
       </c>
       <c r="J64" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K64" s="100" t="n">
@@ -10339,7 +10333,7 @@
       </c>
       <c r="J65" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K65" s="100" t="n">
@@ -10395,7 +10389,7 @@
       </c>
       <c r="J66" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K66" s="100" t="n">
@@ -10455,7 +10449,7 @@
       </c>
       <c r="J67" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K67" s="100" t="n">
@@ -10515,7 +10509,7 @@
       </c>
       <c r="J68" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K68" s="100" t="n">
@@ -10575,7 +10569,7 @@
       </c>
       <c r="J69" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K69" s="100" t="n">
@@ -10635,7 +10629,7 @@
       </c>
       <c r="J70" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K70" s="100" t="n">
@@ -10691,7 +10685,7 @@
       </c>
       <c r="J71" s="94" t="inlineStr">
         <is>
-          <t>吕道远</t>
+          <t>徐蔚</t>
         </is>
       </c>
       <c r="K71" s="100" t="n">

--- a/P1-R03-工期评估表-20260915.xlsx
+++ b/P1-R03-工期评估表-20260915.xlsx
@@ -19,14 +19,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.##"/>
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="m/d"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -314,6 +316,9 @@
     <font>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
     </font>
   </fonts>
   <fills count="56">
@@ -640,7 +645,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -863,6 +868,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E79"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1011,7 +1045,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1246,6 +1280,52 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="53" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="38" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="49" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="49" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="48" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="38" fillId="50" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="38" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="43" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="50" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="43" fillId="50" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1827,27 +1907,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>汇总与折算（公式驱动，唯一维护处）</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="B1" s="105" t="n"/>
+      <c r="C1" s="105" t="n"/>
+      <c r="D1" s="105" t="n"/>
+      <c r="E1" s="105" t="n"/>
+      <c r="F1" s="105" t="n"/>
+      <c r="G1" s="105" t="n"/>
+      <c r="H1" s="105" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="105" t="n"/>
+      <c r="B2" s="105" t="n"/>
+      <c r="C2" s="105" t="n"/>
+      <c r="D2" s="105" t="n"/>
+      <c r="E2" s="105" t="n"/>
+      <c r="F2" s="105" t="n"/>
+      <c r="G2" s="105" t="n"/>
+      <c r="H2" s="105" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="76" t="inlineStr">
         <is>
           <t>WBS</t>
@@ -1878,469 +1975,524 @@
           <t>关键风险/依赖</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="G3" s="105" t="n"/>
+      <c r="H3" s="105" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="93" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B4" s="77" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>需求调研与PRD</t>
         </is>
       </c>
-      <c r="C4" s="78">
+      <c r="C4" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A4,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D4" s="77">
+      <c r="D4" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K4:K7)=0,"",MIN('功能点评估（全栈）'!K4:K7))</f>
         <v/>
       </c>
-      <c r="E4" s="77">
+      <c r="E4" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L4:L7)=0,"",MAX('功能点评估（全栈）'!L4:L7))</f>
         <v/>
       </c>
-      <c r="F4" s="77" t="inlineStr">
+      <c r="F4" s="107" t="inlineStr">
         <is>
           <t>#2 #3 材料未齐即启动，PRD 有返工风险</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="G4" s="88" t="n"/>
+      <c r="H4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="93" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="78" t="inlineStr">
         <is>
           <t>原型设计</t>
         </is>
       </c>
-      <c r="C5" s="78">
+      <c r="C5" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A5,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K8:K9)=0,"",MIN('功能点评估（全栈）'!K8:K9))</f>
         <v/>
       </c>
-      <c r="E5" s="77">
+      <c r="E5" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L8:L9)=0,"",MAX('功能点评估（全栈）'!L8:L9))</f>
         <v/>
       </c>
-      <c r="F5" s="77" t="inlineStr">
+      <c r="F5" s="107" t="inlineStr">
         <is>
           <t>v2.8 已交付，仅评修订量</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="G5" s="88" t="n"/>
+      <c r="H5" s="89" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="93" t="inlineStr">
         <is>
           <t>B0</t>
         </is>
       </c>
-      <c r="B6" s="77" t="inlineStr">
+      <c r="B6" s="78" t="inlineStr">
         <is>
           <t>公共底座与移动端</t>
         </is>
       </c>
-      <c r="C6" s="78">
+      <c r="C6" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A6,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K10:K15)=0,"",MIN('功能点评估（全栈）'!K10:K15))</f>
         <v/>
       </c>
-      <c r="E6" s="77">
+      <c r="E6" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L10:L15)=0,"",MAX('功能点评估（全栈）'!L10:L15))</f>
         <v/>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="77" t="inlineStr">
+      <c r="F6" s="107" t="n"/>
+      <c r="G6" s="88" t="n"/>
+      <c r="H6" s="89" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="93" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B7" s="77" t="inlineStr">
+      <c r="B7" s="78" t="inlineStr">
         <is>
           <t>基础数据</t>
         </is>
       </c>
-      <c r="C7" s="78">
+      <c r="C7" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A7,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K16:K20)=0,"",MIN('功能点评估（全栈）'!K16:K20))</f>
         <v/>
       </c>
-      <c r="E7" s="77">
+      <c r="E7" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L16:L20)=0,"",MAX('功能点评估（全栈）'!L16:L20))</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="F7" s="107" t="n"/>
+      <c r="G7" s="88" t="n"/>
+      <c r="H7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="93" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B8" s="77" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>项目管理中心</t>
         </is>
       </c>
-      <c r="C8" s="78">
+      <c r="C8" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A8,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D8" s="77">
+      <c r="D8" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K21:K25)=0,"",MIN('功能点评估（全栈）'!K21:K25))</f>
         <v/>
       </c>
-      <c r="E8" s="77">
+      <c r="E8" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L21:L25)=0,"",MAX('功能点评估（全栈）'!L21:L25))</f>
         <v/>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="F8" s="107" t="n"/>
+      <c r="G8" s="88" t="n"/>
+      <c r="H8" s="89" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="93" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B9" s="77" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>仓储作业 ★核心</t>
         </is>
       </c>
-      <c r="C9" s="78">
+      <c r="C9" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A9,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K26:K37)=0,"",MIN('功能点评估（全栈）'!K26:K37))</f>
         <v/>
       </c>
-      <c r="E9" s="77">
+      <c r="E9" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L26:L37)=0,"",MAX('功能点评估（全栈）'!L26:L37))</f>
         <v/>
       </c>
-      <c r="F9" s="77" t="inlineStr">
+      <c r="F9" s="107" t="inlineStr">
         <is>
           <t>11 类单据；无组装/拆卸（BOM 结果导向·出库按组合扣减/退租按零件入库）</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="G9" s="88" t="n"/>
+      <c r="H9" s="89" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="93" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B10" s="77" t="inlineStr">
+      <c r="B10" s="78" t="inlineStr">
         <is>
           <t>租赁管理</t>
         </is>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A10,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K38:K42)=0,"",MIN('功能点评估（全栈）'!K38:K42))</f>
         <v/>
       </c>
-      <c r="E10" s="77">
+      <c r="E10" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L38:L42)=0,"",MAX('功能点评估（全栈）'!L38:L42))</f>
         <v/>
       </c>
-      <c r="F10" s="77" t="inlineStr">
+      <c r="F10" s="107" t="inlineStr">
         <is>
           <t>计费定案（09-15·D-145）：按时间周期直录日租金／按次次单价·按持有量计租·三段式仅档案参考价</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="G10" s="88" t="n"/>
+      <c r="H10" s="89" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="93" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B11" s="77" t="inlineStr">
+      <c r="B11" s="78" t="inlineStr">
         <is>
           <t>销售管理</t>
         </is>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A11,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K43:K47)=0,"",MIN('功能点评估（全栈）'!K43:K47))</f>
         <v/>
       </c>
-      <c r="E11" s="77">
+      <c r="E11" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L43:L47)=0,"",MAX('功能点评估（全栈）'!L43:L47))</f>
         <v/>
       </c>
-      <c r="F11" s="77" t="inlineStr">
+      <c r="F11" s="107" t="inlineStr">
         <is>
           <t>#6 路凯对接方式待定</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="G11" s="88" t="n"/>
+      <c r="H11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="93" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>财务协同</t>
         </is>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A12,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K48:K55)=0,"",MIN('功能点评估（全栈）'!K48:K55))</f>
         <v/>
       </c>
-      <c r="E12" s="77">
+      <c r="E12" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L48:L55)=0,"",MAX('功能点评估（全栈）'!L48:L55))</f>
         <v/>
       </c>
-      <c r="F12" s="77" t="inlineStr">
+      <c r="F12" s="107" t="inlineStr">
         <is>
           <t>#5 单据/水单样例、#8 开票主体待提供</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="G12" s="88" t="n"/>
+      <c r="H12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="93" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="78" t="inlineStr">
         <is>
           <t>系统管理</t>
         </is>
       </c>
-      <c r="C13" s="78">
+      <c r="C13" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A13,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K56:K58)=0,"",MIN('功能点评估（全栈）'!K56:K58))</f>
         <v/>
       </c>
-      <c r="E13" s="77">
+      <c r="E13" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L56:L58)=0,"",MAX('功能点评估（全栈）'!L56:L58))</f>
         <v/>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="77" t="inlineStr">
+      <c r="F13" s="107" t="n"/>
+      <c r="G13" s="88" t="n"/>
+      <c r="H13" s="89" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="93" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="B14" s="77" t="inlineStr">
+      <c r="B14" s="78" t="inlineStr">
         <is>
           <t>采购管理</t>
         </is>
       </c>
-      <c r="C14" s="78">
+      <c r="C14" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A14,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D14" s="77">
+      <c r="D14" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K59:K63)=0,"",MIN('功能点评估（全栈）'!K59:K63))</f>
         <v/>
       </c>
-      <c r="E14" s="77">
+      <c r="E14" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L59:L63)=0,"",MAX('功能点评估（全栈）'!L59:L63))</f>
         <v/>
       </c>
-      <c r="F14" s="77" t="inlineStr">
+      <c r="F14" s="107" t="inlineStr">
         <is>
           <t>第 2 次会新增模块（09-04 拍板第一期闭环）</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="G14" s="88" t="n"/>
+      <c r="H14" s="89" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="93" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="B15" s="77" t="inlineStr">
+      <c r="B15" s="78" t="inlineStr">
         <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="C15" s="78">
+      <c r="C15" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A15,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K64:K65)=0,"",MIN('功能点评估（全栈）'!K64:K65))</f>
         <v/>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L64:L65)=0,"",MAX('功能点评估（全栈）'!L64:L65))</f>
         <v/>
       </c>
-      <c r="F15" s="77" t="inlineStr">
+      <c r="F15" s="107" t="inlineStr">
         <is>
           <t>用例需覆盖 F01 五条主线全链路</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="G15" s="88" t="n"/>
+      <c r="H15" s="89" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="93" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="78" t="inlineStr">
         <is>
           <t>数据迁移</t>
         </is>
       </c>
-      <c r="C16" s="78">
+      <c r="C16" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A16,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D16" s="77">
+      <c r="D16" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K66:K68)=0,"",MIN('功能点评估（全栈）'!K66:K68))</f>
         <v/>
       </c>
-      <c r="E16" s="77">
+      <c r="E16" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L66:L68)=0,"",MAX('功能点评估（全栈）'!L66:L68))</f>
         <v/>
       </c>
-      <c r="F16" s="77" t="inlineStr">
+      <c r="F16" s="107" t="inlineStr">
         <is>
           <t>#4 主数据清单与格式待提供</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="77" t="inlineStr">
+      <c r="G16" s="88" t="n"/>
+      <c r="H16" s="89" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="93" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="B17" s="77" t="inlineStr">
+      <c r="B17" s="78" t="inlineStr">
         <is>
           <t>上线部署</t>
         </is>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="95">
         <f>SUMIF('功能点评估（全栈）'!$A$4:$A$76,$A17,'功能点评估（全栈）'!$H$4:$H$76)</f>
         <v/>
       </c>
-      <c r="D17" s="77">
+      <c r="D17" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!K69:K71)=0,"",MIN('功能点评估（全栈）'!K69:K71))</f>
         <v/>
       </c>
-      <c r="E17" s="77">
+      <c r="E17" s="106">
         <f>IF(COUNT('功能点评估（全栈）'!L69:L71)=0,"",MAX('功能点评估（全栈）'!L69:L71))</f>
         <v/>
       </c>
-      <c r="F17" s="77" t="inlineStr">
+      <c r="F17" s="107" t="inlineStr">
         <is>
           <t>试运行窗口待与客户确认</t>
         </is>
       </c>
+      <c r="G17" s="88" t="n"/>
+      <c r="H17" s="89" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="77" t="inlineStr">
+      <c r="A18" s="105" t="n"/>
+      <c r="B18" s="108" t="inlineStr">
         <is>
           <t>合计 / 全跨度</t>
         </is>
       </c>
-      <c r="C18" s="78">
+      <c r="C18" s="109">
         <f>SUM(C4:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="77">
+      <c r="D18" s="108">
         <f>IF(COUNT(D4:D17)=0,"",MIN(D4:D17))</f>
         <v/>
       </c>
-      <c r="E18" s="77">
+      <c r="E18" s="108">
         <f>IF(COUNT(E4:E17)=0,"",MAX(E4:E17))</f>
         <v/>
       </c>
+      <c r="F18" s="105" t="n"/>
+      <c r="G18" s="105" t="n"/>
+      <c r="H18" s="105" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="105" t="n"/>
+      <c r="B19" s="105" t="n"/>
+      <c r="C19" s="105" t="n"/>
+      <c r="D19" s="105" t="n"/>
+      <c r="E19" s="105" t="n"/>
+      <c r="F19" s="105" t="n"/>
+      <c r="G19" s="105" t="n"/>
+      <c r="H19" s="105" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="76" t="inlineStr">
+      <c r="A20" s="110" t="inlineStr">
         <is>
           <t>版本里程碑（人日 × 上线节点 × 范围，合并原「版本小计 + 里程碑一览」）</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="77" t="inlineStr">
+      <c r="B20" s="111" t="n"/>
+      <c r="C20" s="111" t="n"/>
+      <c r="D20" s="111" t="n"/>
+      <c r="E20" s="111" t="n"/>
+      <c r="F20" s="111" t="n"/>
+      <c r="G20" s="111" t="n"/>
+      <c r="H20" s="111" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>版本</t>
         </is>
       </c>
-      <c r="B21" s="77" t="inlineStr">
+      <c r="B21" s="76" t="inlineStr">
         <is>
           <t>上线 / 完成节点</t>
         </is>
       </c>
-      <c r="C21" s="78" t="inlineStr">
+      <c r="C21" s="76" t="inlineStr">
         <is>
           <t>范围与业务</t>
         </is>
       </c>
-      <c r="D21" s="77" t="inlineStr">
+      <c r="D21" s="76" t="inlineStr">
         <is>
           <t>人日小计</t>
         </is>
       </c>
-      <c r="E21" s="77" t="inlineStr">
+      <c r="E21" s="76" t="inlineStr">
         <is>
           <t>含缓冲</t>
         </is>
       </c>
-      <c r="F21" s="77" t="inlineStr">
+      <c r="F21" s="76" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="G21" s="77" t="inlineStr">
+      <c r="G21" s="76" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="H21" s="77" t="inlineStr">
+      <c r="H21" s="76" t="inlineStr">
         <is>
           <t>无AI对照
 （方案1·约219人日）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="77" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="94" t="inlineStr">
         <is>
           <t>前置</t>
         </is>
       </c>
-      <c r="B22" s="77" t="inlineStr">
+      <c r="B22" s="94" t="inlineStr">
         <is>
           <t>09-02 ~ 09-18 定版</t>
         </is>
@@ -2350,32 +2502,32 @@
           <t>需求 09-02 起（第 2~4 次沟通＋09-15 拍板包）+ 计费定案（按天计租）+ PRD 冻结 + 芋道底座/编码规范</t>
         </is>
       </c>
-      <c r="D22" s="79" t="n">
+      <c r="D22" s="112" t="n">
         <v>12.75</v>
       </c>
-      <c r="E22" s="79">
+      <c r="E22" s="112">
         <f>ROUND(D22*(1+$C$46),2)</f>
         <v/>
       </c>
-      <c r="F22" s="80" t="n">
+      <c r="F22" s="106" t="n">
         <v>46267</v>
       </c>
-      <c r="G22" s="80" t="n">
+      <c r="G22" s="106" t="n">
         <v>46283</v>
       </c>
-      <c r="H22" s="77" t="inlineStr">
+      <c r="H22" s="94" t="inlineStr">
         <is>
           <t>无AI 09-23</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="77" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <t>V1.0</t>
         </is>
       </c>
-      <c r="B23" s="77" t="inlineStr">
+      <c r="B23" s="94" t="inlineStr">
         <is>
           <t>★ 10-20 上线（09-15 增补·初估）</t>
         </is>
@@ -2385,32 +2537,32 @@
           <t>买卖版：买卖全链 + 库存（查询五态/调拨/其他出入库）+ 应收六来源/回款 + 权限矩阵；+库存事件流水/采购退货/销售退货（09-15 增·人日待评估）</t>
         </is>
       </c>
-      <c r="D23" s="79" t="n">
+      <c r="D23" s="112" t="n">
         <v>41</v>
       </c>
-      <c r="E23" s="79">
+      <c r="E23" s="112">
         <f>ROUND(D23*(1+$C$46),2)</f>
         <v/>
       </c>
-      <c r="F23" s="80" t="n">
+      <c r="F23" s="106" t="n">
         <v>46275</v>
       </c>
-      <c r="G23" s="80" t="n">
+      <c r="G23" s="106" t="n">
         <v>46295</v>
       </c>
-      <c r="H23" s="77" t="inlineStr">
+      <c r="H23" s="94" t="inlineStr">
         <is>
           <t>无AI 11-03</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="77" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="94" t="inlineStr">
         <is>
           <t>V1.1</t>
         </is>
       </c>
-      <c r="B24" s="77" t="inlineStr">
+      <c r="B24" s="94" t="inlineStr">
         <is>
           <t>★ 11-24 上线（初估）</t>
         </is>
@@ -2420,32 +2572,32 @@
           <t>租赁版：租赁循环（租赁单/租赁出库/退租入库两事件）+ BOM + 按天计租（直录日租金） + 应付/付款 + 移动端 H5；+转移出库/按持有量计租/退款登记（09-15 增·人日待评估）</t>
         </is>
       </c>
-      <c r="D24" s="79" t="n">
+      <c r="D24" s="112" t="n">
         <v>34.5</v>
       </c>
-      <c r="E24" s="79">
+      <c r="E24" s="112">
         <f>ROUND(D24*(1+$C$46),2)</f>
         <v/>
       </c>
-      <c r="F24" s="80" t="n">
+      <c r="F24" s="106" t="n">
         <v>46282</v>
       </c>
-      <c r="G24" s="80" t="n">
+      <c r="G24" s="106" t="n">
         <v>46338</v>
       </c>
-      <c r="H24" s="77" t="inlineStr">
+      <c r="H24" s="94" t="inlineStr">
         <is>
           <t>无AI 12-17</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="77" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>V2.0</t>
         </is>
       </c>
-      <c r="B25" s="77" t="inlineStr">
+      <c r="B25" s="94" t="inlineStr">
         <is>
           <t>★ 12-14 上线（初估）</t>
         </is>
@@ -2455,32 +2607,32 @@
           <t>深化版：租入三单（L3/L4）+ 路凯对接 + 财务收口（开票/银行回单核销/财务看板）+ 数据字典</t>
         </is>
       </c>
-      <c r="D25" s="79" t="n">
+      <c r="D25" s="112" t="n">
         <v>20.5</v>
       </c>
-      <c r="E25" s="79">
+      <c r="E25" s="112">
         <f>ROUND(D25*(1+$C$46),2)</f>
         <v/>
       </c>
-      <c r="F25" s="80" t="n">
+      <c r="F25" s="106" t="n">
         <v>46339</v>
       </c>
-      <c r="G25" s="80" t="n">
+      <c r="G25" s="106" t="n">
         <v>46356</v>
       </c>
-      <c r="H25" s="77" t="inlineStr">
+      <c r="H25" s="94" t="inlineStr">
         <is>
           <t>无AI 01-22</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="77" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="94" t="inlineStr">
         <is>
           <t>验收收口</t>
         </is>
       </c>
-      <c r="B26" s="77" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
         <is>
           <t>01-08 前后（初估）</t>
         </is>
@@ -2490,21 +2642,23 @@
           <t>试运行 2 周（真实订单并行）+ 01-08 前验收；富余产能启动 2027 backlog</t>
         </is>
       </c>
-      <c r="D26" s="81" t="n"/>
-      <c r="E26" s="81" t="n"/>
-      <c r="H26" s="77" t="inlineStr">
+      <c r="D26" s="113" t="n"/>
+      <c r="E26" s="113" t="n"/>
+      <c r="F26" s="105" t="n"/>
+      <c r="G26" s="105" t="n"/>
+      <c r="H26" s="94" t="inlineStr">
         <is>
           <t>无AI 2027-02-05</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="77" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="94" t="inlineStr">
         <is>
           <t>各版</t>
         </is>
       </c>
-      <c r="B27" s="77" t="inlineStr">
+      <c r="B27" s="94" t="inlineStr">
         <is>
           <t>10-13 / 11-16 / 12-08 启动（初估）</t>
         </is>
@@ -2514,335 +2668,507 @@
           <t>测试 / UAT / 数据迁移 / 部署 / 切换 / 试运行——每版上线前各跑一轮（单轮 15 人日×3）</t>
         </is>
       </c>
-      <c r="D27" s="79" t="n">
+      <c r="D27" s="112" t="n">
         <v>45</v>
       </c>
-      <c r="E27" s="79">
+      <c r="E27" s="112">
         <f>ROUND(D27*(1+$C$46),2)</f>
         <v/>
       </c>
-      <c r="F27" s="80" t="n">
+      <c r="F27" s="106" t="n">
         <v>46308</v>
       </c>
-      <c r="G27" s="80" t="n">
+      <c r="G27" s="106" t="n">
         <v>46381</v>
       </c>
-      <c r="H27" s="77" t="inlineStr">
+      <c r="H27" s="94" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="82" t="inlineStr">
+      <c r="A28" s="105" t="n"/>
+      <c r="B28" s="105" t="n"/>
+      <c r="C28" s="114" t="inlineStr">
         <is>
           <t>版本人日合计（校验=总合计 C18）</t>
         </is>
       </c>
-      <c r="D28" s="83">
+      <c r="D28" s="115">
         <f>SUM(D22:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="83">
+      <c r="E28" s="115">
         <f>IF(D28=C18,"✓ 一致","✗ 不一致")</f>
         <v/>
       </c>
+      <c r="F28" s="105" t="n"/>
+      <c r="G28" s="105" t="n"/>
+      <c r="H28" s="105" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="105" t="n"/>
+      <c r="B29" s="105" t="n"/>
+      <c r="C29" s="105" t="n"/>
+      <c r="D29" s="105" t="n"/>
+      <c r="E29" s="105" t="n"/>
+      <c r="F29" s="105" t="n"/>
+      <c r="G29" s="105" t="n"/>
+      <c r="H29" s="105" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="A30" s="110" t="inlineStr">
         <is>
           <t>按月负载（原「按月版本规划」主体并入）</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="77" t="inlineStr">
+      <c r="B30" s="111" t="n"/>
+      <c r="C30" s="111" t="n"/>
+      <c r="D30" s="111" t="n"/>
+      <c r="E30" s="111" t="n"/>
+      <c r="F30" s="111" t="n"/>
+      <c r="G30" s="111" t="n"/>
+      <c r="H30" s="111" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="76" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="B31" s="77" t="inlineStr">
+      <c r="B31" s="76" t="inlineStr">
         <is>
           <t>计划人日
 （含缓冲）</t>
         </is>
       </c>
-      <c r="C31" s="78" t="inlineStr">
+      <c r="C31" s="76" t="inlineStr">
         <is>
           <t>当月产能
 （人日）</t>
         </is>
       </c>
-      <c r="D31" s="77" t="inlineStr">
+      <c r="D31" s="76" t="inlineStr">
         <is>
           <t>负载率</t>
         </is>
       </c>
-      <c r="E31" s="77" t="inlineStr">
+      <c r="E31" s="76" t="inlineStr">
         <is>
           <t>当月里程碑与内容摘要</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="F31" s="105" t="n"/>
+      <c r="G31" s="105" t="n"/>
+      <c r="H31" s="105" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="94" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B32" s="77" t="n">
+      <c r="B32" s="95" t="n">
         <v>46</v>
       </c>
-      <c r="C32" s="78" t="n">
+      <c r="C32" s="95" t="n">
         <v>54</v>
       </c>
-      <c r="D32" s="77">
+      <c r="D32" s="116">
         <f>B32/C32</f>
         <v/>
       </c>
-      <c r="E32" s="77" t="inlineStr">
+      <c r="E32" s="78" t="inlineStr">
         <is>
           <t>需求 09-18 冻结；底座+V1.0 全量开发（09-15 起）＋采购/销售退货单与库存事件流水并入</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="77" t="inlineStr">
+      <c r="F32" s="88" t="n"/>
+      <c r="G32" s="88" t="n"/>
+      <c r="H32" s="89" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="94" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B33" s="77" t="n">
+      <c r="B33" s="95" t="n">
         <v>47.5</v>
       </c>
-      <c r="C33" s="78" t="n">
+      <c r="C33" s="95" t="n">
         <v>48</v>
       </c>
-      <c r="D33" s="77">
+      <c r="D33" s="116">
         <f>B33/C33</f>
         <v/>
       </c>
-      <c r="E33" s="77" t="inlineStr">
+      <c r="E33" s="78" t="inlineStr">
         <is>
           <t>10-13~20 轮1：集成测试/UAT/主数据迁移/部署；★10-20 V1.0 上线（09-15 增补口径·初估）</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="77" t="inlineStr">
+      <c r="F33" s="88" t="n"/>
+      <c r="G33" s="88" t="n"/>
+      <c r="H33" s="89" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="94" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B34" s="77" t="n">
+      <c r="B34" s="95" t="n">
         <v>46</v>
       </c>
-      <c r="C34" s="78" t="n">
+      <c r="C34" s="95" t="n">
         <v>63</v>
       </c>
-      <c r="D34" s="77">
+      <c r="D34" s="116">
         <f>B34/C34</f>
         <v/>
       </c>
-      <c r="E34" s="77" t="inlineStr">
+      <c r="E34" s="78" t="inlineStr">
         <is>
           <t>V1.1 开发完成（含移动端 H5＋转移出库＋按天计租引擎＋退款登记）；11-16~23 轮2；★11-24 V1.1 上线</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="77" t="inlineStr">
+      <c r="F34" s="88" t="n"/>
+      <c r="G34" s="88" t="n"/>
+      <c r="H34" s="89" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="94" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B35" s="77" t="n">
+      <c r="B35" s="95" t="n">
         <v>37.31</v>
       </c>
-      <c r="C35" s="78" t="n">
+      <c r="C35" s="95" t="n">
         <v>69</v>
       </c>
-      <c r="D35" s="77">
+      <c r="D35" s="116">
         <f>B35/C35</f>
         <v/>
       </c>
-      <c r="E35" s="77" t="inlineStr">
+      <c r="E35" s="78" t="inlineStr">
         <is>
           <t>12-08~11 轮3（租入在途迁移/部署）；★12-14 V2.0 全量上线（128+ 页口径）；01-08 前验收</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="77" t="inlineStr">
+      <c r="F35" s="88" t="n"/>
+      <c r="G35" s="88" t="n"/>
+      <c r="H35" s="89" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="93" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B36" s="77">
+      <c r="B36" s="117">
         <f>SUM(B32:B35)</f>
         <v/>
       </c>
-      <c r="C36" s="78">
+      <c r="C36" s="117">
         <f>SUM(C32:C35)</f>
         <v/>
       </c>
-      <c r="D36" s="77">
+      <c r="D36" s="118">
         <f>B36/C36</f>
         <v/>
       </c>
+      <c r="E36" s="105" t="n"/>
+      <c r="F36" s="88" t="n"/>
+      <c r="G36" s="88" t="n"/>
+      <c r="H36" s="89" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="105" t="n"/>
+      <c r="B37" s="105" t="n"/>
+      <c r="C37" s="105" t="n"/>
+      <c r="D37" s="105" t="n"/>
+      <c r="E37" s="105" t="n"/>
+      <c r="F37" s="105" t="n"/>
+      <c r="G37" s="105" t="n"/>
+      <c r="H37" s="105" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="77" t="inlineStr">
+      <c r="A38" s="119" t="inlineStr">
         <is>
           <t>AI 协作（Claude Code）前提与风险</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="77" t="inlineStr">
+      <c r="B38" s="111" t="n"/>
+      <c r="C38" s="111" t="n"/>
+      <c r="D38" s="111" t="n"/>
+      <c r="E38" s="111" t="n"/>
+      <c r="F38" s="111" t="n"/>
+      <c r="G38" s="111" t="n"/>
+      <c r="H38" s="111" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="93" t="inlineStr">
         <is>
           <t>R1 评审带宽</t>
         </is>
       </c>
-      <c r="B39" s="77" t="inlineStr">
+      <c r="B39" s="93" t="inlineStr">
         <is>
           <t>AI 产出量大，3 名工程师须固定每日代码评审时段消化</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="77" t="inlineStr">
+      <c r="C39" s="107" t="n"/>
+      <c r="D39" s="88" t="n"/>
+      <c r="E39" s="88" t="n"/>
+      <c r="F39" s="88" t="n"/>
+      <c r="G39" s="88" t="n"/>
+      <c r="H39" s="89" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="93" t="inlineStr">
         <is>
           <t>R2 风格统一</t>
         </is>
       </c>
-      <c r="B40" s="77" t="inlineStr">
+      <c r="B40" s="93" t="inlineStr">
         <is>
           <t>底座周（09-09~10）必须落编码规范与组件约定，统一三套 AI 风格</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="77" t="inlineStr">
+      <c r="C40" s="107" t="n"/>
+      <c r="D40" s="88" t="n"/>
+      <c r="E40" s="88" t="n"/>
+      <c r="F40" s="88" t="n"/>
+      <c r="G40" s="88" t="n"/>
+      <c r="H40" s="89" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="93" t="inlineStr">
         <is>
           <t>R3 关键逻辑</t>
         </is>
       </c>
-      <c r="B41" s="77" t="inlineStr">
+      <c r="B41" s="93" t="inlineStr">
         <is>
           <t>库存过账/组装拆卸/四态计费/水单核销以人工设计主导，勿盲信 AI 产出</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="77" t="inlineStr">
+      <c r="C41" s="107" t="n"/>
+      <c r="D41" s="88" t="n"/>
+      <c r="E41" s="88" t="n"/>
+      <c r="F41" s="88" t="n"/>
+      <c r="G41" s="88" t="n"/>
+      <c r="H41" s="89" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="93" t="inlineStr">
         <is>
           <t>R4 磨合回退</t>
         </is>
       </c>
-      <c r="B42" s="77" t="inlineStr">
+      <c r="B42" s="93" t="inlineStr">
         <is>
           <t>若 AI 协作磨合不顺（提速退化），工期按 约 219 人日口径上浮，里程碑顺延</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="77" t="inlineStr">
+      <c r="C42" s="107" t="n"/>
+      <c r="D42" s="88" t="n"/>
+      <c r="E42" s="88" t="n"/>
+      <c r="F42" s="88" t="n"/>
+      <c r="G42" s="88" t="n"/>
+      <c r="H42" s="89" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="93" t="inlineStr">
         <is>
           <t>R5 外部依赖</t>
         </is>
       </c>
-      <c r="B43" s="77" t="inlineStr">
+      <c r="B43" s="93" t="inlineStr">
         <is>
           <t>#6 路凯对接方式、#5 水单样例、#8 开票主体——未定项集中在 V2.0 前必须落实</t>
         </is>
       </c>
+      <c r="C43" s="107" t="n"/>
+      <c r="D43" s="88" t="n"/>
+      <c r="E43" s="88" t="n"/>
+      <c r="F43" s="88" t="n"/>
+      <c r="G43" s="88" t="n"/>
+      <c r="H43" s="89" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="105" t="n"/>
+      <c r="B44" s="105" t="n"/>
+      <c r="C44" s="105" t="n"/>
+      <c r="D44" s="105" t="n"/>
+      <c r="E44" s="105" t="n"/>
+      <c r="F44" s="105" t="n"/>
+      <c r="G44" s="105" t="n"/>
+      <c r="H44" s="105" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="77" t="inlineStr">
+      <c r="A45" s="119" t="inlineStr">
         <is>
           <t>参数与折算</t>
         </is>
       </c>
+      <c r="B45" s="111" t="n"/>
+      <c r="C45" s="111" t="n"/>
+      <c r="D45" s="111" t="n"/>
+      <c r="E45" s="111" t="n"/>
+      <c r="F45" s="111" t="n"/>
+      <c r="G45" s="111" t="n"/>
+      <c r="H45" s="111" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="77" t="inlineStr">
+      <c r="A46" s="78" t="inlineStr">
         <is>
           <t>缓冲比例</t>
         </is>
       </c>
-      <c r="C46" s="84" t="n">
+      <c r="B46" s="105" t="n"/>
+      <c r="C46" s="120" t="n">
         <v>0.15</v>
       </c>
-      <c r="D46" s="77" t="inlineStr">
+      <c r="D46" s="107" t="inlineStr">
         <is>
           <t>已填 15%（覆盖联调与管理裕度）</t>
         </is>
       </c>
+      <c r="E46" s="88" t="n"/>
+      <c r="F46" s="88" t="n"/>
+      <c r="G46" s="88" t="n"/>
+      <c r="H46" s="89" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="77" t="inlineStr">
+      <c r="A47" s="78" t="inlineStr">
         <is>
           <t>投入人数</t>
         </is>
       </c>
-      <c r="C47" s="84" t="n">
+      <c r="B47" s="105" t="n"/>
+      <c r="C47" s="120" t="n">
         <v>3</v>
       </c>
-      <c r="D47" s="77" t="inlineStr">
+      <c r="D47" s="107" t="inlineStr">
         <is>
           <t>已填 3（对应 P1-R01 第八节 #9）</t>
         </is>
       </c>
+      <c r="E47" s="88" t="n"/>
+      <c r="F47" s="88" t="n"/>
+      <c r="G47" s="88" t="n"/>
+      <c r="H47" s="89" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="77" t="inlineStr">
+      <c r="A48" s="78" t="inlineStr">
         <is>
           <t>每月工作日</t>
         </is>
       </c>
-      <c r="C48" s="84" t="n">
+      <c r="B48" s="105" t="n"/>
+      <c r="C48" s="120" t="n">
         <v>21</v>
       </c>
-      <c r="D48" s="77" t="inlineStr">
+      <c r="D48" s="107" t="inlineStr">
         <is>
           <t>人月折算基准</t>
         </is>
       </c>
+      <c r="E48" s="88" t="n"/>
+      <c r="F48" s="88" t="n"/>
+      <c r="G48" s="88" t="n"/>
+      <c r="H48" s="89" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="77" t="inlineStr">
+      <c r="A49" s="78" t="inlineStr">
         <is>
           <t>含缓冲合计（人日）</t>
         </is>
       </c>
-      <c r="C49" s="78">
+      <c r="B49" s="105" t="n"/>
+      <c r="C49" s="120">
         <f>IF(OR($C$46="",$C$18=0),"",$C$18*(1+$C$46))</f>
         <v/>
       </c>
-      <c r="D49" s="77" t="inlineStr">
+      <c r="D49" s="107" t="inlineStr">
         <is>
           <t>自动：合计×(1+缓冲)</t>
         </is>
       </c>
+      <c r="E49" s="88" t="n"/>
+      <c r="F49" s="88" t="n"/>
+      <c r="G49" s="88" t="n"/>
+      <c r="H49" s="89" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="77" t="inlineStr">
+      <c r="A50" s="78" t="inlineStr">
         <is>
           <t>日历工期（月）</t>
         </is>
       </c>
-      <c r="C50" s="78">
+      <c r="B50" s="105" t="n"/>
+      <c r="C50" s="121">
         <f>IF(OR($C$46="",$C$47="",$C$47=0,$C$49=""),"",$C$49/($C$48*$C$47))</f>
         <v/>
       </c>
-      <c r="D50" s="77" t="inlineStr">
+      <c r="D50" s="107" t="inlineStr">
         <is>
           <t>自动</t>
         </is>
       </c>
+      <c r="E50" s="88" t="n"/>
+      <c r="F50" s="88" t="n"/>
+      <c r="G50" s="88" t="n"/>
+      <c r="H50" s="89" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="78" t="n"/>
+      <c r="B51" s="105" t="n"/>
+      <c r="C51" s="121" t="n"/>
+      <c r="D51" s="107" t="n"/>
+      <c r="E51" s="88" t="n"/>
+      <c r="F51" s="88" t="n"/>
+      <c r="G51" s="88" t="n"/>
+      <c r="H51" s="89" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="E36:H36"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/P1-R03-工期评估表-20260915.xlsx
+++ b/P1-R03-工期评估表-20260915.xlsx
@@ -2430,7 +2430,7 @@
       <c r="H19" s="105" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="110" t="inlineStr">
+      <c r="A20" s="119" t="inlineStr">
         <is>
           <t>版本里程碑（人日 × 上线节点 × 范围，合并原「版本小计 + 里程碑一览」）</t>
         </is>
@@ -2718,7 +2718,7 @@
       <c r="H29" s="105" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="110" t="inlineStr">
+      <c r="A30" s="119" t="inlineStr">
         <is>
           <t>按月负载（原「按月版本规划」主体并入）</t>
         </is>

--- a/P1-R03-工期评估表-20260915.xlsx
+++ b/P1-R03-工期评估表-20260915.xlsx
@@ -6502,7 +6502,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -9407,6 +9407,18 @@
         <v>405</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【G41 注记·2026-09-16】</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>G37 转移出库／G38 字段口径／G39 按天计租 三任务增量工作量按 D-135 只注记不重算；本表数字维持 V20260915（D-94）口径。增量明细见 P2-R01 决策台账 D-146~D-150 与对应任务档（agent-handoff/）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/P1-R03-工期评估表-20260915.xlsx
+++ b/P1-R03-工期评估表-20260915.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="23810" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="版本交付阶梯图" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="408">
   <si>
     <t>汇总与折算（公式驱动，唯一维护处）</t>
   </si>
@@ -1258,6 +1258,12 @@
   </si>
   <si>
     <t>每版预留试运行窗口；依赖 #4 主数据清单；V1.0 前导客商/器具/零部件，V1.1 前导 BOM 与在租</t>
+  </si>
+  <si>
+    <t>【G41 注记·2026-09-16】</t>
+  </si>
+  <si>
+    <t>G37 转移出库／G38 字段口径／G39 按天计租 三任务增量工作量按 D-135 只注记不重算；本表数字维持 V20260915（D-94）口径。增量明细见 P2-R01 决策台账 D-146~D-150 与对应任务档（agent-handoff/）。</t>
   </si>
 </sst>
 </file>
@@ -2281,13 +2287,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>551815</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>161290</xdr:rowOff>
+      <xdr:colOff>120015</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>33655</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPr id="5" name="图片 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2301,7 +2307,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6350" y="6350"/>
-          <a:ext cx="15175865" cy="10822940"/>
+          <a:ext cx="14744065" cy="10517505"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9407,16 +9413,12 @@
         <v>405</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>【G41 注记·2026-09-16】</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>G37 转移出库／G38 字段口径／G39 按天计租 三任务增量工作量按 D-135 只注记不重算；本表数字维持 V20260915（D-94）口径。增量明细见 P2-R01 决策台账 D-146~D-150 与对应任务档（agent-handoff/）。</t>
-        </is>
+    <row r="72" spans="1:13">
+      <c r="A72" t="s">
+        <v>406</v>
+      </c>
+      <c r="B72" t="s">
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/P1-R03-工期评估表-20260915.xlsx
+++ b/P1-R03-工期评估表-20260915.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="407">
   <si>
     <t>汇总与折算（公式驱动，唯一维护处）</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>试运行窗口待与客户确认</t>
-  </si>
-  <si>
-    <t>合计 / 全跨度</t>
   </si>
   <si>
     <t>版本里程碑（人日 × 上线节点 × 范围，合并原「版本小计 + 里程碑一览」）</t>
@@ -1742,7 +1739,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1783,21 +1780,6 @@
       </right>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF1F4E79"/>
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
@@ -1941,7 +1923,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
@@ -1953,34 +1935,34 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="9">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="9">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="11">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
@@ -2065,7 +2047,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2129,12 +2111,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2143,10 +2119,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2620,7 +2596,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3020,302 +2996,302 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="24"/>
-      <c r="B18" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="28">
-        <f>SUM(C4:C17)</f>
-        <v>153.75</v>
-      </c>
-      <c r="D18" s="27">
-        <f>IF(COUNT(D4:D17)=0,"",MIN(D4:D17))</f>
-        <v>46267</v>
-      </c>
-      <c r="E18" s="27">
-        <f>IF(COUNT(E4:E17)=0,"",MAX(E4:E17))</f>
-        <v>46381</v>
-      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-    </row>
-    <row r="20" ht="117" spans="1:8">
-      <c r="A20" s="29" t="s">
+    <row r="19" ht="117" spans="1:8">
+      <c r="A19" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:8">
+      <c r="A20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:8">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:8">
+      <c r="A21" s="5" t="s">
         <v>51</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="29">
+        <v>12.75</v>
+      </c>
+      <c r="E21" s="29">
+        <f>ROUND(D21*(1+$C$45),2)</f>
+        <v>14.66</v>
+      </c>
+      <c r="F21" s="25">
+        <v>46267</v>
+      </c>
+      <c r="G21" s="25">
+        <v>46283</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:8">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="31">
-        <v>12.75</v>
-      </c>
-      <c r="E22" s="31">
-        <f>ROUND(D22*(1+$C$46),2)</f>
-        <v>14.66</v>
+        <v>57</v>
+      </c>
+      <c r="D22" s="29">
+        <v>41</v>
+      </c>
+      <c r="E22" s="29">
+        <f>ROUND(D22*(1+$C$45),2)</f>
+        <v>47.15</v>
       </c>
       <c r="F22" s="25">
-        <v>46267</v>
+        <v>46275</v>
       </c>
       <c r="G22" s="25">
-        <v>46283</v>
+        <v>46295</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:8">
       <c r="A23" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="31">
-        <v>41</v>
-      </c>
-      <c r="E23" s="31">
-        <f>ROUND(D23*(1+$C$46),2)</f>
-        <v>47.15</v>
+        <v>61</v>
+      </c>
+      <c r="D23" s="29">
+        <v>34.5</v>
+      </c>
+      <c r="E23" s="29">
+        <f>ROUND(D23*(1+$C$45),2)</f>
+        <v>39.68</v>
       </c>
       <c r="F23" s="25">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="G23" s="25">
-        <v>46295</v>
+        <v>46338</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:8">
       <c r="A24" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="31">
-        <v>34.5</v>
-      </c>
-      <c r="E24" s="31">
-        <f>ROUND(D24*(1+$C$46),2)</f>
-        <v>39.68</v>
+        <v>65</v>
+      </c>
+      <c r="D24" s="29">
+        <v>20.5</v>
+      </c>
+      <c r="E24" s="29">
+        <f>ROUND(D24*(1+$C$45),2)</f>
+        <v>23.58</v>
       </c>
       <c r="F24" s="25">
-        <v>46282</v>
+        <v>46339</v>
       </c>
       <c r="G24" s="25">
-        <v>46338</v>
+        <v>46356</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:8">
       <c r="A25" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="31">
-        <v>20.5</v>
-      </c>
-      <c r="E25" s="31">
-        <f>ROUND(D25*(1+$C$46),2)</f>
-        <v>23.58</v>
-      </c>
-      <c r="F25" s="25">
-        <v>46339</v>
-      </c>
-      <c r="G25" s="25">
-        <v>46356</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:8">
       <c r="A26" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
+        <v>73</v>
+      </c>
+      <c r="D26" s="29">
+        <v>45</v>
+      </c>
+      <c r="E26" s="29">
+        <f>ROUND(D26*(1+$C$45),2)</f>
+        <v>51.75</v>
+      </c>
+      <c r="F26" s="25">
+        <v>46308</v>
+      </c>
+      <c r="G26" s="25">
+        <v>46381</v>
+      </c>
       <c r="H26" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1" spans="1:8">
-      <c r="A27" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="31">
-        <v>45</v>
-      </c>
-      <c r="E27" s="31">
-        <f>ROUND(D27*(1+$C$46),2)</f>
-        <v>51.75</v>
-      </c>
-      <c r="F27" s="25">
-        <v>46308</v>
-      </c>
-      <c r="G27" s="25">
-        <v>46381</v>
-      </c>
-      <c r="H27" s="5" t="s">
+    </row>
+    <row r="27" ht="14.75" spans="1:8">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="31" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="28" ht="14.75" spans="1:8">
+      <c r="D27" s="32">
+        <f>SUM(D21:D26)</f>
+        <v>153.75</v>
+      </c>
+      <c r="E27" s="32" t="e">
+        <f>IF(D27=#REF!,"✓ 一致","✗ 不一致")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="24"/>
       <c r="B28" s="24"/>
-      <c r="C28" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="34">
-        <f>SUM(D22:D27)</f>
-        <v>153.75</v>
-      </c>
-      <c r="E28" s="34" t="str">
-        <f>IF(D28=C18,"✓ 一致","✗ 不一致")</f>
-        <v>✓ 一致</v>
-      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-    </row>
-    <row r="30" ht="65" spans="1:8">
-      <c r="A30" s="29" t="s">
+    <row r="29" ht="65" spans="1:8">
+      <c r="A29" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:8">
+      <c r="A30" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:8">
-      <c r="A31" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:8">
+      <c r="A31" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
+      <c r="B31" s="8">
+        <v>46</v>
+      </c>
+      <c r="C31" s="8">
+        <v>54</v>
+      </c>
+      <c r="D31" s="33">
+        <f>B31/C31</f>
+        <v>0.851851851851852</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:8">
       <c r="A32" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" s="8">
-        <v>46</v>
+        <v>47.5</v>
       </c>
       <c r="C32" s="8">
-        <v>54</v>
-      </c>
-      <c r="D32" s="35">
+        <v>48</v>
+      </c>
+      <c r="D32" s="33">
         <f>B32/C32</f>
-        <v>0.851851851851852</v>
+        <v>0.989583333333333</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F32" s="15"/>
       <c r="G32" s="15"/>
@@ -3323,20 +3299,20 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8">
       <c r="A33" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="8">
-        <v>47.5</v>
+        <v>46</v>
       </c>
       <c r="C33" s="8">
-        <v>48</v>
-      </c>
-      <c r="D33" s="35">
+        <v>63</v>
+      </c>
+      <c r="D33" s="33">
         <f>B33/C33</f>
-        <v>0.989583333333333</v>
+        <v>0.73015873015873</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
@@ -3344,95 +3320,88 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8">
       <c r="A34" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B34" s="8">
-        <v>46</v>
+        <v>37.31</v>
       </c>
       <c r="C34" s="8">
-        <v>63</v>
-      </c>
-      <c r="D34" s="35">
+        <v>69</v>
+      </c>
+      <c r="D34" s="33">
         <f>B34/C34</f>
-        <v>0.73015873015873</v>
+        <v>0.540724637681159</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="16"/>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8">
-      <c r="A35" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" s="8">
-        <v>37.31</v>
-      </c>
-      <c r="C35" s="8">
-        <v>69</v>
+      <c r="A35" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="34">
+        <f>SUM(B31:B34)</f>
+        <v>176.81</v>
+      </c>
+      <c r="C35" s="34">
+        <f>SUM(C31:C34)</f>
+        <v>234</v>
       </c>
       <c r="D35" s="35">
         <f>B35/C35</f>
-        <v>0.540724637681159</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>0.755598290598291</v>
+      </c>
+      <c r="E35" s="24"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" ht="22" customHeight="1" spans="1:8">
-      <c r="A36" s="20" t="s">
+    <row r="36" spans="1:8">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+    </row>
+    <row r="37" ht="52" spans="1:8">
+      <c r="A37" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="36">
-        <f>SUM(B32:B35)</f>
-        <v>176.81</v>
-      </c>
-      <c r="C36" s="36">
-        <f>SUM(C32:C35)</f>
-        <v>234</v>
-      </c>
-      <c r="D36" s="37">
-        <f>B36/C36</f>
-        <v>0.755598290598291</v>
-      </c>
-      <c r="E36" s="24"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="16"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-    </row>
-    <row r="38" ht="52" spans="1:8">
-      <c r="A38" s="29" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:8">
+      <c r="A38" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
+      <c r="B38" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="26"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="16"/>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:8">
       <c r="A39" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="15"/>
@@ -3443,10 +3412,10 @@
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:8">
       <c r="A40" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C40" s="26"/>
       <c r="D40" s="15"/>
@@ -3457,10 +3426,10 @@
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:8">
       <c r="A41" s="20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="15"/>
@@ -3471,10 +3440,10 @@
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:8">
       <c r="A42" s="20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" s="26"/>
       <c r="D42" s="15"/>
@@ -3483,52 +3452,54 @@
       <c r="G42" s="15"/>
       <c r="H42" s="16"/>
     </row>
-    <row r="43" ht="20" customHeight="1" spans="1:8">
-      <c r="A43" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B43" s="20" t="s">
+    <row r="43" spans="1:8">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+    </row>
+    <row r="44" ht="26" spans="1:8">
+      <c r="A44" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="26"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="16"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-    </row>
-    <row r="45" ht="26" spans="1:8">
-      <c r="A45" s="29" t="s">
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="36">
+        <v>0.15</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="24"/>
-      <c r="C46" s="38">
-        <v>0.15</v>
+      <c r="C46" s="36">
+        <v>3</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="15"/>
@@ -3537,30 +3508,31 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="24"/>
-      <c r="C47" s="38">
-        <v>3</v>
+      <c r="C47" s="36">
+        <v>21</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="15"/>
       <c r="G47" s="15"/>
       <c r="H47" s="16"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" ht="24" spans="1:8">
       <c r="A48" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="24"/>
-      <c r="C48" s="38">
-        <v>21</v>
+      <c r="C48" s="36" t="e">
+        <f>IF(OR($C$45="",#REF!=0),"",#REF!*(1+$C$45))</f>
+        <v>#REF!</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E48" s="15"/>
       <c r="F48" s="15"/>
@@ -3569,47 +3541,30 @@
     </row>
     <row r="49" ht="24" spans="1:8">
       <c r="A49" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="24"/>
-      <c r="C49" s="38">
-        <f>IF(OR($C$46="",$C$18=0),"",$C$18*(1+$C$46))</f>
-        <v>176.8125</v>
+      <c r="C49" s="37" t="e">
+        <f>IF(OR($C$45="",$C$46="",$C$46=0,$C$48=""),"",$C$48/($C$47*$C$46))</f>
+        <v>#REF!</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="15"/>
       <c r="G49" s="15"/>
       <c r="H49" s="16"/>
     </row>
-    <row r="50" ht="24" spans="1:8">
-      <c r="A50" s="6" t="s">
-        <v>112</v>
-      </c>
+    <row r="50" spans="1:8">
+      <c r="A50" s="6"/>
       <c r="B50" s="24"/>
-      <c r="C50" s="39">
-        <f>IF(OR($C$46="",$C$47="",$C$47=0,$C$49=""),"",$C$49/($C$48*$C$47))</f>
-        <v>2.80654761904762</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>113</v>
-      </c>
+      <c r="C50" s="37"/>
+      <c r="D50" s="26"/>
       <c r="E50" s="15"/>
       <c r="F50" s="15"/>
       <c r="G50" s="15"/>
       <c r="H50" s="16"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -3627,22 +3582,22 @@
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="F17:H17"/>
+    <mergeCell ref="E31:H31"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="E33:H33"/>
     <mergeCell ref="E34:H34"/>
     <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="C38:H38"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="D45:H45"/>
     <mergeCell ref="D46:H46"/>
     <mergeCell ref="D47:H47"/>
     <mergeCell ref="D48:H48"/>
     <mergeCell ref="D49:H49"/>
     <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3665,12 +3620,12 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:83">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:83">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1" spans="1:83">
@@ -3678,19 +3633,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>119</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>120</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
@@ -3713,7 +3668,7 @@
       <c r="Y3" s="15"/>
       <c r="Z3" s="16"/>
       <c r="AA3" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AB3" s="15"/>
       <c r="AC3" s="15"/>
@@ -3732,7 +3687,7 @@
       <c r="AP3" s="15"/>
       <c r="AQ3" s="16"/>
       <c r="AR3" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AS3" s="15"/>
       <c r="AT3" s="15"/>
@@ -3755,7 +3710,7 @@
       <c r="BK3" s="15"/>
       <c r="BL3" s="16"/>
       <c r="BM3" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BN3" s="15"/>
       <c r="BO3" s="15"/>
@@ -4014,7 +3969,7 @@
     </row>
     <row r="5" spans="1:83">
       <c r="A5" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -4024,10 +3979,10 @@
     </row>
     <row r="6" spans="1:83">
       <c r="A6" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" s="8">
         <v>6</v>
@@ -4041,10 +3996,10 @@
     </row>
     <row r="7" spans="1:83">
       <c r="A7" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="8">
         <v>1</v>
@@ -4058,10 +4013,10 @@
     </row>
     <row r="8" spans="1:83">
       <c r="A8" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="8">
         <v>5.75</v>
@@ -4075,7 +4030,7 @@
     </row>
     <row r="9" spans="1:83">
       <c r="A9" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -4085,10 +4040,10 @@
     </row>
     <row r="10" spans="1:83">
       <c r="A10" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C10" s="8">
         <v>6.5</v>
@@ -4102,10 +4057,10 @@
     </row>
     <row r="11" spans="1:83">
       <c r="A11" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C11" s="8">
         <v>1.5</v>
@@ -4119,10 +4074,10 @@
     </row>
     <row r="12" spans="1:83">
       <c r="A12" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C12" s="8">
         <v>14</v>
@@ -4136,10 +4091,10 @@
     </row>
     <row r="13" spans="1:83">
       <c r="A13" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="8">
         <v>4.5</v>
@@ -4153,10 +4108,10 @@
     </row>
     <row r="14" spans="1:83">
       <c r="A14" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="8">
         <v>5</v>
@@ -4170,10 +4125,10 @@
     </row>
     <row r="15" spans="1:83">
       <c r="A15" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="8">
         <v>1.5</v>
@@ -4187,10 +4142,10 @@
     </row>
     <row r="16" spans="1:83">
       <c r="A16" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="8">
         <v>8</v>
@@ -4204,7 +4159,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -4214,10 +4169,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="8">
         <v>3</v>
@@ -4231,10 +4186,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C19" s="8">
         <v>5</v>
@@ -4248,10 +4203,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C20" s="8">
         <v>7.5</v>
@@ -4265,10 +4220,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21" s="8">
         <v>11</v>
@@ -4282,10 +4237,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C22" s="8">
         <v>6</v>
@@ -4299,10 +4254,10 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C23" s="8">
         <v>2.5</v>
@@ -4316,7 +4271,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -4326,10 +4281,10 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" s="8">
         <v>5</v>
@@ -4343,10 +4298,10 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" s="8">
         <v>6</v>
@@ -4360,10 +4315,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C27" s="8">
         <v>8</v>
@@ -4377,10 +4332,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="8">
         <v>1.5</v>
@@ -4394,7 +4349,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -4404,10 +4359,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C30" s="8">
         <v>17</v>
@@ -4421,10 +4376,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C31" s="8">
         <v>13</v>
@@ -4438,10 +4393,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C32" s="8">
         <v>15</v>
@@ -4520,12 +4475,12 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:85">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:85">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="14.5" customHeight="1" spans="1:85">
@@ -4533,25 +4488,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>154</v>
-      </c>
       <c r="D3" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>119</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>120</v>
       </c>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
@@ -4574,7 +4529,7 @@
       <c r="AA3" s="15"/>
       <c r="AB3" s="16"/>
       <c r="AC3" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AD3" s="15"/>
       <c r="AE3" s="15"/>
@@ -4593,7 +4548,7 @@
       <c r="AR3" s="15"/>
       <c r="AS3" s="16"/>
       <c r="AT3" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AU3" s="15"/>
       <c r="AV3" s="15"/>
@@ -4616,7 +4571,7 @@
       <c r="BM3" s="15"/>
       <c r="BN3" s="16"/>
       <c r="BO3" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BP3" s="15"/>
       <c r="BQ3" s="15"/>
@@ -4875,7 +4830,7 @@
     </row>
     <row r="5" spans="1:85">
       <c r="A5" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -4890,13 +4845,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" s="8">
         <v>1.5</v>
@@ -4913,13 +4868,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" s="8">
         <v>2</v>
@@ -4936,13 +4891,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="8">
         <v>1.5</v>
@@ -4959,13 +4914,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="8">
         <v>1</v>
@@ -4982,13 +4937,13 @@
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="8">
         <v>0.5</v>
@@ -5005,13 +4960,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="8">
         <v>0.5</v>
@@ -5028,13 +4983,13 @@
         <v>13</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="8">
         <v>1.5</v>
@@ -5051,13 +5006,13 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13" s="8">
         <v>0.75</v>
@@ -5074,13 +5029,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E14" s="8">
         <v>3.5</v>
@@ -5094,7 +5049,7 @@
     </row>
     <row r="15" spans="1:85">
       <c r="A15" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -5109,13 +5064,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" s="8">
         <v>0.5</v>
@@ -5132,13 +5087,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="D17" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" s="8">
         <v>1.5</v>
@@ -5155,13 +5110,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>169</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="8">
         <v>2</v>
@@ -5178,13 +5133,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" s="8">
         <v>2</v>
@@ -5201,13 +5156,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="8">
         <v>1</v>
@@ -5224,13 +5179,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>175</v>
-      </c>
       <c r="D21" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" s="8">
         <v>0.5</v>
@@ -5247,13 +5202,13 @@
         <v>17</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>177</v>
-      </c>
       <c r="D22" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" s="8">
         <v>1</v>
@@ -5270,13 +5225,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="D23" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" s="8">
         <v>2</v>
@@ -5293,13 +5248,13 @@
         <v>19</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="D24" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" s="8">
         <v>3</v>
@@ -5316,13 +5271,13 @@
         <v>19</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>183</v>
-      </c>
       <c r="D25" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" s="8">
         <v>2</v>
@@ -5339,13 +5294,13 @@
         <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E26" s="8">
         <v>1.5</v>
@@ -5362,13 +5317,13 @@
         <v>19</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" s="8">
         <v>1.5</v>
@@ -5385,13 +5340,13 @@
         <v>19</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" s="8">
         <v>1.5</v>
@@ -5408,13 +5363,13 @@
         <v>19</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" s="8">
         <v>2.5</v>
@@ -5431,13 +5386,13 @@
         <v>25</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="D30" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" s="8">
         <v>2</v>
@@ -5454,13 +5409,13 @@
         <v>25</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>191</v>
-      </c>
       <c r="D31" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E31" s="8">
         <v>1</v>
@@ -5477,13 +5432,13 @@
         <v>25</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E32" s="8">
         <v>1.5</v>
@@ -5500,13 +5455,13 @@
         <v>28</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" s="8">
         <v>3</v>
@@ -5523,13 +5478,13 @@
         <v>28</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="D34" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" s="8">
         <v>1.5</v>
@@ -5546,13 +5501,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>198</v>
-      </c>
       <c r="D35" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E35" s="8">
         <v>1.5</v>
@@ -5569,13 +5524,13 @@
         <v>33</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="D36" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E36" s="8">
         <v>2</v>
@@ -5592,13 +5547,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="D37" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E37" s="8">
         <v>1</v>
@@ -5626,13 +5581,13 @@
         <v>33</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="D39" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E39" s="8">
         <v>1.5</v>
@@ -5649,13 +5604,13 @@
         <v>33</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E40" s="8">
         <v>1.5</v>
@@ -5669,7 +5624,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -5684,13 +5639,13 @@
         <v>13</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" s="8">
         <v>2.5</v>
@@ -5707,13 +5662,13 @@
         <v>13</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="21"/>
@@ -5724,13 +5679,13 @@
         <v>15</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>210</v>
-      </c>
       <c r="D44" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E44" s="8">
         <v>3</v>
@@ -5747,13 +5702,13 @@
         <v>17</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>212</v>
-      </c>
       <c r="D45" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" s="8">
         <v>1.5</v>
@@ -5770,13 +5725,13 @@
         <v>17</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>214</v>
-      </c>
       <c r="D46" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" s="8">
         <v>1.5</v>
@@ -5793,13 +5748,13 @@
         <v>17</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" s="8">
         <v>2</v>
@@ -5816,13 +5771,13 @@
         <v>19</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>217</v>
-      </c>
       <c r="D48" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E48" s="8">
         <v>2</v>
@@ -5839,13 +5794,13 @@
         <v>19</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="D49" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E49" s="8">
         <v>2.5</v>
@@ -5862,13 +5817,13 @@
         <v>19</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>221</v>
-      </c>
       <c r="D50" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" s="8">
         <v>3</v>
@@ -5885,13 +5840,13 @@
         <v>22</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>223</v>
-      </c>
       <c r="D51" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" s="8">
         <v>3</v>
@@ -5908,13 +5863,13 @@
         <v>22</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="D52" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E52" s="8">
         <v>3</v>
@@ -5931,13 +5886,13 @@
         <v>22</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E53" s="8">
         <v>2</v>
@@ -5954,13 +5909,13 @@
         <v>22</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="8">
         <v>2.5</v>
@@ -5977,13 +5932,13 @@
         <v>28</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>229</v>
-      </c>
       <c r="D55" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" s="8">
         <v>2.5</v>
@@ -6000,13 +5955,13 @@
         <v>28</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>231</v>
-      </c>
       <c r="D56" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E56" s="8">
         <v>1.5</v>
@@ -6031,7 +5986,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -6046,13 +6001,13 @@
         <v>19</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E59" s="8">
         <v>1.5</v>
@@ -6069,13 +6024,13 @@
         <v>19</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E60" s="8">
         <v>1.5</v>
@@ -6092,13 +6047,13 @@
         <v>22</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E61" s="8">
         <v>2</v>
@@ -6115,13 +6070,13 @@
         <v>25</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="D62" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E62" s="8">
         <v>4</v>
@@ -6138,13 +6093,13 @@
         <v>25</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>239</v>
-      </c>
       <c r="D63" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E63" s="8">
         <v>2</v>
@@ -6161,13 +6116,13 @@
         <v>28</v>
       </c>
       <c r="B64" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="D64" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E64" s="8">
         <v>1.5</v>
@@ -6184,13 +6139,13 @@
         <v>28</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>243</v>
-      </c>
       <c r="D65" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E65" s="8">
         <v>4</v>
@@ -6207,13 +6162,13 @@
         <v>28</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>245</v>
-      </c>
       <c r="D66" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E66" s="8">
         <v>2.5</v>
@@ -6230,13 +6185,13 @@
         <v>31</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>247</v>
-      </c>
       <c r="D67" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E67" s="8">
         <v>0.5</v>
@@ -6261,7 +6216,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -6276,13 +6231,13 @@
         <v>36</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E70" s="8">
         <v>10</v>
@@ -6299,13 +6254,13 @@
         <v>36</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E71" s="8">
         <v>7</v>
@@ -6322,13 +6277,13 @@
         <v>39</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E72" s="8">
         <v>4</v>
@@ -6345,13 +6300,13 @@
         <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E73" s="8">
         <v>6</v>
@@ -6368,13 +6323,13 @@
         <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E74" s="8">
         <v>3</v>
@@ -6391,13 +6346,13 @@
         <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E75" s="8">
         <v>3</v>
@@ -6414,13 +6369,13 @@
         <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E76" s="8">
         <v>5</v>
@@ -6437,13 +6392,13 @@
         <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E77" s="8">
         <v>7</v>
@@ -6528,12 +6483,12 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" ht="39" spans="1:13">
@@ -6544,37 +6499,37 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="E3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:13">
@@ -6585,29 +6540,29 @@
         <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>267</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H4" s="8">
         <v>1.5</v>
       </c>
       <c r="I4" s="8">
-        <f>H4*(1+汇总!$C$46)</f>
+        <f>H4*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K4" s="9">
         <v>46267</v>
@@ -6616,7 +6571,7 @@
         <v>46279</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:13">
@@ -6627,29 +6582,29 @@
         <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5" s="8">
         <v>2</v>
       </c>
       <c r="I5" s="8">
-        <f>H5*(1+汇总!$C$46)</f>
+        <f>H5*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K5" s="9">
         <v>46274</v>
@@ -6658,7 +6613,7 @@
         <v>46280</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" ht="24" spans="1:13">
@@ -6669,29 +6624,29 @@
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H6" s="8">
         <v>1.5</v>
       </c>
       <c r="I6" s="8">
-        <f>H6*(1+汇总!$C$46)</f>
+        <f>H6*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K6" s="9">
         <v>46274</v>
@@ -6700,7 +6655,7 @@
         <v>46275</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:13">
@@ -6711,29 +6666,29 @@
         <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
       </c>
       <c r="I7" s="8">
-        <f>H7*(1+汇总!$C$46)</f>
+        <f>H7*(1+汇总!$C$45)</f>
         <v>1.15</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K7" s="9">
         <v>46276</v>
@@ -6742,7 +6697,7 @@
         <v>46283</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:13">
@@ -6753,29 +6708,29 @@
         <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>276</v>
-      </c>
       <c r="G8" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="8">
         <v>0.5</v>
       </c>
       <c r="I8" s="8">
-        <f>H8*(1+汇总!$C$46)</f>
+        <f>H8*(1+汇总!$C$45)</f>
         <v>0.575</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K8" s="9">
         <v>46279</v>
@@ -6784,7 +6739,7 @@
         <v>46283</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" ht="36" spans="1:13">
@@ -6795,29 +6750,29 @@
         <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" s="8">
         <v>0.5</v>
       </c>
       <c r="I9" s="8">
-        <f>H9*(1+汇总!$C$46)</f>
+        <f>H9*(1+汇总!$C$45)</f>
         <v>0.575</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K9" s="9">
         <v>46283</v>
@@ -6826,7 +6781,7 @@
         <v>46283</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" ht="24" spans="1:13">
@@ -6837,29 +6792,29 @@
         <v>14</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" s="8">
         <v>1.5</v>
       </c>
       <c r="I10" s="8">
-        <f>H10*(1+汇总!$C$46)</f>
+        <f>H10*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K10" s="9">
         <v>46272</v>
@@ -6868,7 +6823,7 @@
         <v>46273</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" ht="36" spans="1:13">
@@ -6879,29 +6834,29 @@
         <v>14</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" s="8">
         <v>0.75</v>
       </c>
       <c r="I11" s="8">
-        <f>H11*(1+汇总!$C$46)</f>
+        <f>H11*(1+汇总!$C$45)</f>
         <v>0.8625</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K11" s="9">
         <v>46274</v>
@@ -6910,7 +6865,7 @@
         <v>46274</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" ht="36" spans="1:13">
@@ -6921,29 +6876,29 @@
         <v>14</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12" s="8">
         <v>3.5</v>
       </c>
       <c r="I12" s="8">
-        <f>H12*(1+汇总!$C$46)</f>
+        <f>H12*(1+汇总!$C$45)</f>
         <v>4.025</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K12" s="9">
         <v>46274</v>
@@ -6952,7 +6907,7 @@
         <v>46275</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" ht="24" spans="1:13">
@@ -6963,29 +6918,29 @@
         <v>14</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H13" s="8">
         <v>0.5</v>
       </c>
       <c r="I13" s="8">
-        <f>H13*(1+汇总!$C$46)</f>
+        <f>H13*(1+汇总!$C$45)</f>
         <v>0.575</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K13" s="9">
         <v>46293</v>
@@ -6994,7 +6949,7 @@
         <v>46293</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" ht="24" spans="1:13">
@@ -7005,29 +6960,29 @@
         <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14" s="8">
         <v>2.5</v>
       </c>
       <c r="I14" s="8">
-        <f>H14*(1+汇总!$C$46)</f>
+        <f>H14*(1+汇总!$C$45)</f>
         <v>2.875</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K14" s="9">
         <v>46314</v>
@@ -7036,7 +6991,7 @@
         <v>46318</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" ht="24" spans="1:13">
@@ -7047,32 +7002,32 @@
         <v>14</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>292</v>
-      </c>
       <c r="G15" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8">
-        <f>H15*(1+汇总!$C$46)</f>
+        <f>H15*(1+汇总!$C$45)</f>
         <v>0</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -7083,29 +7038,29 @@
         <v>16</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>167</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H16" s="8">
         <v>1.5</v>
       </c>
       <c r="I16" s="8">
-        <f>H16*(1+汇总!$C$46)</f>
+        <f>H16*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K16" s="9">
         <v>46275</v>
@@ -7123,29 +7078,29 @@
         <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>169</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="8">
         <v>2</v>
       </c>
       <c r="I17" s="8">
-        <f>H17*(1+汇总!$C$46)</f>
+        <f>H17*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K17" s="9">
         <v>46279</v>
@@ -7163,29 +7118,29 @@
         <v>16</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>297</v>
-      </c>
       <c r="G18" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H18" s="8">
         <v>2</v>
       </c>
       <c r="I18" s="8">
-        <f>H18*(1+汇总!$C$46)</f>
+        <f>H18*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K18" s="9">
         <v>46281</v>
@@ -7194,7 +7149,7 @@
         <v>46282</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" ht="24" spans="1:13">
@@ -7205,29 +7160,29 @@
         <v>16</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="E19" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H19" s="8">
         <v>3</v>
       </c>
       <c r="I19" s="8">
-        <f>H19*(1+汇总!$C$46)</f>
+        <f>H19*(1+汇总!$C$45)</f>
         <v>3.45</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K19" s="9">
         <v>46314</v>
@@ -7236,7 +7191,7 @@
         <v>46316</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" ht="24" spans="1:13">
@@ -7247,29 +7202,29 @@
         <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>302</v>
-      </c>
       <c r="G20" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20" s="8">
         <v>1</v>
       </c>
       <c r="I20" s="8">
-        <f>H20*(1+汇总!$C$46)</f>
+        <f>H20*(1+汇总!$C$45)</f>
         <v>1.15</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K20" s="9">
         <v>46283</v>
@@ -7278,7 +7233,7 @@
         <v>46283</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -7289,29 +7244,29 @@
         <v>18</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="E21" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="8">
         <v>0.5</v>
       </c>
       <c r="I21" s="8">
-        <f>H21*(1+汇总!$C$46)</f>
+        <f>H21*(1+汇总!$C$45)</f>
         <v>0.575</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K21" s="9">
         <v>46275</v>
@@ -7329,29 +7284,29 @@
         <v>18</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>177</v>
-      </c>
       <c r="E22" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H22" s="8">
         <v>1</v>
       </c>
       <c r="I22" s="8">
-        <f>H22*(1+汇总!$C$46)</f>
+        <f>H22*(1+汇总!$C$45)</f>
         <v>1.15</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K22" s="9">
         <v>46276</v>
@@ -7360,7 +7315,7 @@
         <v>46276</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" ht="24" spans="1:13">
@@ -7371,29 +7326,29 @@
         <v>18</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>212</v>
-      </c>
       <c r="E23" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H23" s="8">
         <v>1.5</v>
       </c>
       <c r="I23" s="8">
-        <f>H23*(1+汇总!$C$46)</f>
+        <f>H23*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K23" s="9">
         <v>46290</v>
@@ -7402,7 +7357,7 @@
         <v>46293</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" ht="24" spans="1:13">
@@ -7413,29 +7368,29 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>214</v>
-      </c>
       <c r="E24" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H24" s="8">
         <v>1.5</v>
       </c>
       <c r="I24" s="8">
-        <f>H24*(1+汇总!$C$46)</f>
+        <f>H24*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K24" s="9">
         <v>46294</v>
@@ -7444,7 +7399,7 @@
         <v>46295</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" ht="36" spans="1:13">
@@ -7455,29 +7410,29 @@
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>312</v>
-      </c>
       <c r="G25" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H25" s="8">
         <v>2</v>
       </c>
       <c r="I25" s="8">
-        <f>H25*(1+汇总!$C$46)</f>
+        <f>H25*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K25" s="9">
         <v>46304</v>
@@ -7486,7 +7441,7 @@
         <v>46308</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" ht="36" spans="1:13">
@@ -7497,29 +7452,29 @@
         <v>20</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="E26" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H26" s="8">
         <v>2</v>
       </c>
       <c r="I26" s="8">
-        <f>H26*(1+汇总!$C$46)</f>
+        <f>H26*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K26" s="9">
         <v>46276</v>
@@ -7528,7 +7483,7 @@
         <v>46279</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" ht="36" spans="1:13">
@@ -7539,29 +7494,29 @@
         <v>20</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>217</v>
-      </c>
       <c r="E27" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H27" s="8">
         <v>2</v>
       </c>
       <c r="I27" s="8">
-        <f>H27*(1+汇总!$C$46)</f>
+        <f>H27*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K27" s="9">
         <v>46321</v>
@@ -7570,7 +7525,7 @@
         <v>46322</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" ht="36" spans="1:13">
@@ -7581,29 +7536,29 @@
         <v>20</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>219</v>
-      </c>
       <c r="E28" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H28" s="8">
         <v>2.5</v>
       </c>
       <c r="I28" s="8">
-        <f>H28*(1+汇总!$C$46)</f>
+        <f>H28*(1+汇总!$C$45)</f>
         <v>2.875</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K28" s="9">
         <v>46323</v>
@@ -7612,7 +7567,7 @@
         <v>46325</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" ht="24" spans="1:13">
@@ -7623,29 +7578,29 @@
         <v>20</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="E29" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H29" s="8">
         <v>3</v>
       </c>
       <c r="I29" s="8">
-        <f>H29*(1+汇总!$C$46)</f>
+        <f>H29*(1+汇总!$C$45)</f>
         <v>3.45</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K29" s="9">
         <v>46309</v>
@@ -7654,7 +7609,7 @@
         <v>46311</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" ht="24" spans="1:13">
@@ -7665,29 +7620,29 @@
         <v>20</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="E30" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H30" s="8">
         <v>3</v>
       </c>
       <c r="I30" s="8">
-        <f>H30*(1+汇总!$C$46)</f>
+        <f>H30*(1+汇总!$C$45)</f>
         <v>3.45</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K30" s="9">
         <v>46280</v>
@@ -7696,7 +7651,7 @@
         <v>46281</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -7707,29 +7662,29 @@
         <v>20</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="E31" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H31" s="8">
         <v>2</v>
       </c>
       <c r="I31" s="8">
-        <f>H31*(1+汇总!$C$46)</f>
+        <f>H31*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K31" s="9">
         <v>46282</v>
@@ -7738,7 +7693,7 @@
         <v>46283</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" ht="24" spans="1:13">
@@ -7749,29 +7704,29 @@
         <v>20</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H32" s="8">
         <v>1.5</v>
       </c>
       <c r="I32" s="8">
-        <f>H32*(1+汇总!$C$46)</f>
+        <f>H32*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K32" s="9">
         <v>46286</v>
@@ -7780,7 +7735,7 @@
         <v>46287</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -7791,29 +7746,29 @@
         <v>20</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H33" s="8">
         <v>1.5</v>
       </c>
       <c r="I33" s="8">
-        <f>H33*(1+汇总!$C$46)</f>
+        <f>H33*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K33" s="9">
         <v>46288</v>
@@ -7822,7 +7777,7 @@
         <v>46289</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -7833,29 +7788,29 @@
         <v>20</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H34" s="8">
         <v>1.5</v>
       </c>
       <c r="I34" s="8">
-        <f>H34*(1+汇总!$C$46)</f>
+        <f>H34*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K34" s="9">
         <v>46290</v>
@@ -7864,7 +7819,7 @@
         <v>46293</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -7875,29 +7830,29 @@
         <v>20</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H35" s="8">
         <v>1.5</v>
       </c>
       <c r="I35" s="8">
-        <f>H35*(1+汇总!$C$46)</f>
+        <f>H35*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K35" s="9">
         <v>46344</v>
@@ -7906,7 +7861,7 @@
         <v>46345</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="36" ht="24" spans="1:13">
@@ -7917,29 +7872,29 @@
         <v>20</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H36" s="8">
         <v>1.5</v>
       </c>
       <c r="I36" s="8">
-        <f>H36*(1+汇总!$C$46)</f>
+        <f>H36*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K36" s="9">
         <v>46346</v>
@@ -7948,7 +7903,7 @@
         <v>46349</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="37" ht="36" spans="1:13">
@@ -7959,29 +7914,29 @@
         <v>20</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>335</v>
-      </c>
       <c r="G37" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H37" s="8">
         <v>2.5</v>
       </c>
       <c r="I37" s="8">
-        <f>H37*(1+汇总!$C$46)</f>
+        <f>H37*(1+汇总!$C$45)</f>
         <v>2.875</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K37" s="9">
         <v>46290</v>
@@ -7990,7 +7945,7 @@
         <v>46293</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" ht="36" spans="1:13">
@@ -8001,29 +7956,29 @@
         <v>23</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D38" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>338</v>
-      </c>
       <c r="G38" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H38" s="8">
         <v>3.5</v>
       </c>
       <c r="I38" s="8">
-        <f>H38*(1+汇总!$C$46)</f>
+        <f>H38*(1+汇总!$C$45)</f>
         <v>4.025</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K38" s="9">
         <v>46307</v>
@@ -8032,7 +7987,7 @@
         <v>46310</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39" ht="36" spans="1:13">
@@ -8043,29 +7998,29 @@
         <v>23</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>225</v>
-      </c>
       <c r="E39" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H39" s="8">
         <v>3</v>
       </c>
       <c r="I39" s="8">
-        <f>H39*(1+汇总!$C$46)</f>
+        <f>H39*(1+汇总!$C$45)</f>
         <v>3.45</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K39" s="9">
         <v>46314</v>
@@ -8074,7 +8029,7 @@
         <v>46316</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -8085,29 +8040,29 @@
         <v>23</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H40" s="8">
         <v>2</v>
       </c>
       <c r="I40" s="8">
-        <f>H40*(1+汇总!$C$46)</f>
+        <f>H40*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K40" s="9">
         <v>46339</v>
@@ -8116,7 +8071,7 @@
         <v>46343</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" ht="36" spans="1:13">
@@ -8127,29 +8082,29 @@
         <v>23</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D41" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>345</v>
-      </c>
       <c r="G41" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H41" s="8">
         <v>2.5</v>
       </c>
       <c r="I41" s="8">
-        <f>H41*(1+汇总!$C$46)</f>
+        <f>H41*(1+汇总!$C$45)</f>
         <v>2.875</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K41" s="9">
         <v>46324</v>
@@ -8158,7 +8113,7 @@
         <v>46328</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" ht="36" spans="1:13">
@@ -8169,29 +8124,29 @@
         <v>23</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D42" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="G42" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H42" s="8">
         <v>2</v>
       </c>
       <c r="I42" s="8">
-        <f>H42*(1+汇总!$C$46)</f>
+        <f>H42*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K42" s="9">
         <v>46321</v>
@@ -8200,7 +8155,7 @@
         <v>46323</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" ht="36" spans="1:13">
@@ -8211,29 +8166,29 @@
         <v>26</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>189</v>
-      </c>
       <c r="E43" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H43" s="8">
         <v>2</v>
       </c>
       <c r="I43" s="8">
-        <f>H43*(1+汇总!$C$46)</f>
+        <f>H43*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K43" s="9">
         <v>46276</v>
@@ -8242,7 +8197,7 @@
         <v>46279</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" ht="24" spans="1:13">
@@ -8253,29 +8208,29 @@
         <v>26</v>
       </c>
       <c r="C44" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="E44" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H44" s="8">
         <v>1</v>
       </c>
       <c r="I44" s="8">
-        <f>H44*(1+汇总!$C$46)</f>
+        <f>H44*(1+汇总!$C$45)</f>
         <v>1.15</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K44" s="9">
         <v>46281</v>
@@ -8284,7 +8239,7 @@
         <v>46281</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45" ht="24" spans="1:13">
@@ -8295,29 +8250,29 @@
         <v>26</v>
       </c>
       <c r="C45" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>237</v>
-      </c>
       <c r="E45" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H45" s="8">
         <v>4</v>
       </c>
       <c r="I45" s="8">
-        <f>H45*(1+汇总!$C$46)</f>
+        <f>H45*(1+汇总!$C$45)</f>
         <v>4.6</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K45" s="9">
         <v>46344</v>
@@ -8326,7 +8281,7 @@
         <v>46350</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" ht="24" spans="1:13">
@@ -8337,29 +8292,29 @@
         <v>26</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>239</v>
-      </c>
       <c r="E46" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H46" s="8">
         <v>2</v>
       </c>
       <c r="I46" s="8">
-        <f>H46*(1+汇总!$C$46)</f>
+        <f>H46*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K46" s="9">
         <v>46342</v>
@@ -8368,7 +8323,7 @@
         <v>46343</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" ht="24" spans="1:13">
@@ -8379,29 +8334,29 @@
         <v>26</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H47" s="8">
         <v>1.5</v>
       </c>
       <c r="I47" s="8">
-        <f>H47*(1+汇总!$C$46)</f>
+        <f>H47*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K47" s="9">
         <v>46288</v>
@@ -8410,7 +8365,7 @@
         <v>46289</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" ht="36" spans="1:13">
@@ -8421,29 +8376,29 @@
         <v>29</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D48" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>360</v>
-      </c>
       <c r="G48" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H48" s="8">
         <v>3.5</v>
       </c>
       <c r="I48" s="8">
-        <f>H48*(1+汇总!$C$46)</f>
+        <f>H48*(1+汇总!$C$45)</f>
         <v>4.025</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K48" s="9">
         <v>46282</v>
@@ -8452,7 +8407,7 @@
         <v>46286</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -8463,29 +8418,29 @@
         <v>29</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>241</v>
-      </c>
       <c r="E49" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H49" s="8">
         <v>1.5</v>
       </c>
       <c r="I49" s="8">
-        <f>H49*(1+汇总!$C$46)</f>
+        <f>H49*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K49" s="9">
         <v>46344</v>
@@ -8494,7 +8449,7 @@
         <v>46345</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -8505,29 +8460,29 @@
         <v>29</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>196</v>
-      </c>
       <c r="E50" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H50" s="8">
         <v>1.5</v>
       </c>
       <c r="I50" s="8">
-        <f>H50*(1+汇总!$C$46)</f>
+        <f>H50*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K50" s="9">
         <v>46287</v>
@@ -8536,7 +8491,7 @@
         <v>46288</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51" ht="24" spans="1:13">
@@ -8547,29 +8502,29 @@
         <v>29</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D51" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>367</v>
-      </c>
       <c r="G51" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H51" s="8">
         <v>4</v>
       </c>
       <c r="I51" s="8">
-        <f>H51*(1+汇总!$C$46)</f>
+        <f>H51*(1+汇总!$C$45)</f>
         <v>4.6</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K51" s="9">
         <v>46350</v>
@@ -8578,7 +8533,7 @@
         <v>46356</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -8589,29 +8544,29 @@
         <v>29</v>
       </c>
       <c r="C52" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>245</v>
-      </c>
       <c r="E52" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H52" s="8">
         <v>2.5</v>
       </c>
       <c r="I52" s="8">
-        <f>H52*(1+汇总!$C$46)</f>
+        <f>H52*(1+汇总!$C$45)</f>
         <v>2.875</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K52" s="9">
         <v>46350</v>
@@ -8620,7 +8575,7 @@
         <v>46352</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53" ht="36" spans="1:13">
@@ -8631,29 +8586,29 @@
         <v>29</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>229</v>
-      </c>
       <c r="E53" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H53" s="8">
         <v>3</v>
       </c>
       <c r="I53" s="8">
-        <f>H53*(1+汇总!$C$46)</f>
+        <f>H53*(1+汇总!$C$45)</f>
         <v>3.45</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K53" s="9">
         <v>46282</v>
@@ -8662,7 +8617,7 @@
         <v>46287</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -8673,29 +8628,29 @@
         <v>29</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>231</v>
-      </c>
       <c r="E54" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H54" s="8">
         <v>1.5</v>
       </c>
       <c r="I54" s="8">
-        <f>H54*(1+汇总!$C$46)</f>
+        <f>H54*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K54" s="9">
         <v>46288</v>
@@ -8704,7 +8659,7 @@
         <v>46289</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" ht="24" spans="1:13">
@@ -8715,29 +8670,29 @@
         <v>29</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D55" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F55" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>376</v>
-      </c>
       <c r="G55" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H55" s="8">
         <v>1</v>
       </c>
       <c r="I55" s="8">
-        <f>H55*(1+汇总!$C$46)</f>
+        <f>H55*(1+汇总!$C$45)</f>
         <v>1.15</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K55" s="9">
         <v>46329</v>
@@ -8746,7 +8701,7 @@
         <v>46330</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="56" ht="48" spans="1:13">
@@ -8757,29 +8712,29 @@
         <v>32</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D56" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F56" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>379</v>
-      </c>
       <c r="G56" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H56" s="8">
         <v>1.5</v>
       </c>
       <c r="I56" s="8">
-        <f>H56*(1+汇总!$C$46)</f>
+        <f>H56*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K56" s="9">
         <v>46289</v>
@@ -8788,7 +8743,7 @@
         <v>46290</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -8799,29 +8754,29 @@
         <v>32</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D57" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>247</v>
-      </c>
       <c r="E57" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H57" s="8">
         <v>0.5</v>
       </c>
       <c r="I57" s="8">
-        <f>H57*(1+汇总!$C$46)</f>
+        <f>H57*(1+汇总!$C$45)</f>
         <v>0.575</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K57" s="9">
         <v>46346</v>
@@ -8830,7 +8785,7 @@
         <v>46346</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58" ht="36" spans="1:13">
@@ -8841,29 +8796,29 @@
         <v>32</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="E58" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F58" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>385</v>
-      </c>
       <c r="G58" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H58" s="8">
         <v>1</v>
       </c>
       <c r="I58" s="8">
-        <f>H58*(1+汇总!$C$46)</f>
+        <f>H58*(1+汇总!$C$45)</f>
         <v>1.15</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K58" s="9">
         <v>46349</v>
@@ -8872,7 +8827,7 @@
         <v>46349</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59" ht="24" spans="1:13">
@@ -8883,29 +8838,29 @@
         <v>34</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="E59" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H59" s="8">
         <v>2</v>
       </c>
       <c r="I59" s="8">
-        <f>H59*(1+汇总!$C$46)</f>
+        <f>H59*(1+汇总!$C$45)</f>
         <v>2.3</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K59" s="9">
         <v>46286</v>
@@ -8914,7 +8869,7 @@
         <v>46287</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -8925,29 +8880,29 @@
         <v>34</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="E60" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H60" s="8">
         <v>1</v>
       </c>
       <c r="I60" s="8">
-        <f>H60*(1+汇总!$C$46)</f>
+        <f>H60*(1+汇总!$C$45)</f>
         <v>1.15</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K60" s="9">
         <v>46288</v>
@@ -8965,29 +8920,29 @@
         <v>34</v>
       </c>
       <c r="C61" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D61" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="E61" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F61" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>392</v>
-      </c>
       <c r="G61" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H61" s="8">
         <v>1.5</v>
       </c>
       <c r="I61" s="8">
-        <f>H61*(1+汇总!$C$46)</f>
+        <f>H61*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K61" s="9">
         <v>46289</v>
@@ -8996,7 +8951,7 @@
         <v>46290</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="62" ht="24" spans="1:13">
@@ -9007,29 +8962,29 @@
         <v>34</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>204</v>
-      </c>
       <c r="E62" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H62" s="8">
         <v>1.5</v>
       </c>
       <c r="I62" s="8">
-        <f>H62*(1+汇总!$C$46)</f>
+        <f>H62*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K62" s="9">
         <v>46293</v>
@@ -9047,29 +9002,29 @@
         <v>34</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H63" s="8">
         <v>1.5</v>
       </c>
       <c r="I63" s="8">
-        <f>H63*(1+汇总!$C$46)</f>
+        <f>H63*(1+汇总!$C$45)</f>
         <v>1.725</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K63" s="9">
         <v>46294</v>
@@ -9078,7 +9033,7 @@
         <v>46295</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" ht="24" spans="1:13">
@@ -9089,29 +9044,29 @@
         <v>37</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H64" s="8">
         <v>10</v>
       </c>
       <c r="I64" s="8">
-        <f>H64*(1+汇总!$C$46)</f>
+        <f>H64*(1+汇总!$C$45)</f>
         <v>11.5</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K64" s="9">
         <v>46308</v>
@@ -9120,7 +9075,7 @@
         <v>46367</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -9131,29 +9086,29 @@
         <v>37</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H65" s="8">
         <v>7</v>
       </c>
       <c r="I65" s="8">
-        <f>H65*(1+汇总!$C$46)</f>
+        <f>H65*(1+汇总!$C$45)</f>
         <v>8.05</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K65" s="9">
         <v>46314</v>
@@ -9171,29 +9126,29 @@
         <v>40</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H66" s="8">
         <v>4</v>
       </c>
       <c r="I66" s="8">
-        <f>H66*(1+汇总!$C$46)</f>
+        <f>H66*(1+汇总!$C$45)</f>
         <v>4.6</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K66" s="9">
         <v>46308</v>
@@ -9202,7 +9157,7 @@
         <v>46365</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" ht="24" spans="1:13">
@@ -9213,29 +9168,29 @@
         <v>40</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H67" s="8">
         <v>6</v>
       </c>
       <c r="I67" s="8">
-        <f>H67*(1+汇总!$C$46)</f>
+        <f>H67*(1+汇总!$C$45)</f>
         <v>6.9</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K67" s="9">
         <v>46311</v>
@@ -9244,7 +9199,7 @@
         <v>46366</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -9255,29 +9210,29 @@
         <v>40</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H68" s="8">
         <v>3</v>
       </c>
       <c r="I68" s="8">
-        <f>H68*(1+汇总!$C$46)</f>
+        <f>H68*(1+汇总!$C$45)</f>
         <v>3.45</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K68" s="9">
         <v>46314</v>
@@ -9286,7 +9241,7 @@
         <v>46367</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="69" ht="36" spans="1:13">
@@ -9297,29 +9252,29 @@
         <v>43</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H69" s="8">
         <v>3</v>
       </c>
       <c r="I69" s="8">
-        <f>H69*(1+汇总!$C$46)</f>
+        <f>H69*(1+汇总!$C$45)</f>
         <v>3.45</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K69" s="9">
         <v>46314</v>
@@ -9328,7 +9283,7 @@
         <v>46367</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -9339,29 +9294,29 @@
         <v>43</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H70" s="8">
         <v>5</v>
       </c>
       <c r="I70" s="8">
-        <f>H70*(1+汇总!$C$46)</f>
+        <f>H70*(1+汇总!$C$45)</f>
         <v>5.75</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K70" s="9">
         <v>46315</v>
@@ -9379,29 +9334,29 @@
         <v>43</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H71" s="8">
         <v>7</v>
       </c>
       <c r="I71" s="8">
-        <f>H71*(1+汇总!$C$46)</f>
+        <f>H71*(1+汇总!$C$45)</f>
         <v>8.05</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K71" s="9">
         <v>46315</v>
@@ -9410,15 +9365,15 @@
         <v>46381</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" t="s">
+        <v>405</v>
+      </c>
+      <c r="B72" t="s">
         <v>406</v>
-      </c>
-      <c r="B72" t="s">
-        <v>407</v>
       </c>
     </row>
   </sheetData>
